--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="183">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>Author.typeId.nullFlavor</t>
@@ -1429,7 +1433,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1437,10 +1441,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1538,17 +1542,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1566,11 +1570,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1621,7 +1625,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1641,17 +1645,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1669,11 +1673,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1724,7 +1728,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1744,17 +1748,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1772,11 +1776,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1785,7 +1789,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1827,7 +1831,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1847,17 +1851,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1875,11 +1879,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1930,7 +1934,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1950,10 +1954,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1980,7 +1984,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2031,7 +2035,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2051,10 +2055,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2088,7 +2092,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2110,7 +2114,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2128,7 +2132,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2148,10 +2152,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2185,7 +2189,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2207,7 +2211,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2225,7 +2229,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2245,10 +2249,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2271,7 +2275,7 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2324,7 +2328,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2344,10 +2348,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2445,10 +2449,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2477,7 +2481,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2508,7 +2512,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2526,7 +2530,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2546,17 +2550,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>75</v>
@@ -2574,11 +2578,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2629,7 +2633,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2649,17 +2653,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>80</v>
@@ -2677,11 +2681,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2732,7 +2736,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2752,17 +2756,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2780,11 +2784,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2835,7 +2839,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2855,17 +2859,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -2883,11 +2887,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2938,7 +2942,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2958,10 +2962,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2984,11 +2988,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3039,7 +3043,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3059,10 +3063,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3085,11 +3089,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3140,7 +3144,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3160,17 +3164,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
@@ -3188,11 +3192,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3243,7 +3247,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3263,17 +3267,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3291,11 +3295,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3346,7 +3350,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3366,17 +3370,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3394,11 +3398,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3449,7 +3453,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3469,10 +3473,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3495,7 +3499,7 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -3548,7 +3552,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3568,10 +3572,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3669,10 +3673,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3695,11 +3699,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3750,7 +3754,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3770,10 +3774,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3796,7 +3800,7 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -3849,7 +3853,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="187">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -417,6 +417,10 @@
 </t>
   </si>
   <si>
+    <t>Rôle fonctionnel de l'auteur.
+ A utiliser uniquement si l'auteur est un professionnel.</t>
+  </si>
+  <si>
     <t>Author.functionCode.nullFlavor</t>
   </si>
   <si>
@@ -512,6 +516,9 @@
 </t>
   </si>
   <si>
+    <t>Description du rôle fonctionnel de l'auteur.</t>
+  </si>
+  <si>
     <t>The text or phrase used as the basis for the coding.</t>
   </si>
   <si>
@@ -557,6 +564,9 @@
 </t>
   </si>
   <si>
+    <t>Horodatage de la participation de l’auteur</t>
+  </si>
+  <si>
     <t>Author.time.nullFlavor</t>
   </si>
   <si>
@@ -578,6 +588,9 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedAuthor {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-author}
 </t>
+  </si>
+  <si>
+    <t>Identification de l’auteur</t>
   </si>
 </sst>
 </file>
@@ -2277,7 +2290,9 @@
       <c r="K14" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2348,10 +2363,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2449,10 +2464,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2481,7 +2496,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2512,7 +2527,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2530,7 +2545,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2550,17 +2565,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>75</v>
@@ -2582,7 +2597,7 @@
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2633,7 +2648,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2653,17 +2668,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>80</v>
@@ -2685,7 +2700,7 @@
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2736,7 +2751,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2756,17 +2771,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2788,7 +2803,7 @@
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2839,7 +2854,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2859,17 +2874,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -2891,7 +2906,7 @@
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2942,7 +2957,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2962,10 +2977,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2988,11 +3003,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3043,7 +3058,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3063,10 +3078,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3093,7 +3108,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3144,7 +3159,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3164,17 +3179,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
@@ -3192,11 +3207,13 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L23" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="M23" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3247,7 +3264,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3267,17 +3284,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3295,11 +3312,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3350,7 +3367,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3370,17 +3387,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3398,11 +3415,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3453,7 +3470,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3473,10 +3490,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3499,9 +3516,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="L26" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3552,7 +3571,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3572,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3673,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3699,11 +3718,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3754,7 +3773,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3774,10 +3793,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3800,9 +3819,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L29" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3853,7 +3874,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -417,8 +417,7 @@
 </t>
   </si>
   <si>
-    <t>Rôle fonctionnel de l'auteur.
- A utiliser uniquement si l'auteur est un professionnel.</t>
+    <t>Rôle fonctionnel de l'auteur. A utiliser uniquement si l'auteur est un professionnel.</t>
   </si>
   <si>
     <t>Author.functionCode.nullFlavor</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -417,7 +417,7 @@
 </t>
   </si>
   <si>
-    <t>Rôle fonctionnel de l'auteur. A utiliser uniquement si l'auteur est un professionnel.</t>
+    <t>Rôle fonctionnel de l'auteur.</t>
   </si>
   <si>
     <t>Author.functionCode.nullFlavor</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>author permet d’enregistrer un auteur du document.</t>
+    <t>L'élément de l'en-tête du CDA author permet d’enregistrer un auteur du document.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -417,7 +417,7 @@
 </t>
   </si>
   <si>
-    <t>Rôle fonctionnel de l'auteur.</t>
+    <t>Rôle fonctionnel de l'auteur. A utiliser uniquement si l'auteur est un professionnel.</t>
   </si>
   <si>
     <t>Author.functionCode.nullFlavor</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
